--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/C20.0/RANDOMSEARCH_DETAILS_C20.0.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/C20.0/RANDOMSEARCH_DETAILS_C20.0.xlsx
@@ -413,9 +413,4084 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Compose</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID_Pretraitement</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Code_R_Pretraitement</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Meilleurs_Hyperparam_RF</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>RMSEC</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RMSECV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(1,3,5))</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.9111</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1033</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9678</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.8888</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0474</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.102</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1))</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8928</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.9524</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1056</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,700,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9051</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.0174</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0619</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1091</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,750,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8813</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.0124</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.06510000000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1089</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1000,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9191</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.9964</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0554</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1200,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9502</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.9159</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1036</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.8978</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.0276</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0623</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1097</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9669</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.0151</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9328</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.0047</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0557</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1085</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9271</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.0152</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9026999999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.0155</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0613</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.109</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9321</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.0078</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0558</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1086</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8981</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.0188</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1092</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.0098</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1087</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9432</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.9115</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1033</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9772999999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.9144</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1035</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9157</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.9387</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0604</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1048</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9041</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.9377</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0614</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1048</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.9422</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9288999999999999</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.9345</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1046</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9206</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.9166</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0561</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1036</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9322</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.936</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0562</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1047</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9146</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.9538</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.06610000000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1057</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9472</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.9324</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0522</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1045</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9422</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.9124</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1034</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.908</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1031</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9384</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.928</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0574</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1042</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9115</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.9432</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.0609</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1051</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9529</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.9412</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.105</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9717</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.9295</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1043</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9282</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.9185</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1037</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9224</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.9148</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.0653</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1035</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9499</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.9035</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0522</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1029</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9229000000000001</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.9082</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.06279999999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1031</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9157</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.8999</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1026</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9494</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.9022</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1028</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.8992</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.0653</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1026</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9649</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.9206</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.1038</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9223</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.9194</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1038</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9513</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.8996</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1026</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9229000000000001</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.9088</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.06270000000000001</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.1031</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9157</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.9001</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.1027</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9512</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.9076</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0498</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.1031</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9004</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.9064</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.0654</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.103</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1400,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9318</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.9186</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.1037</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(40,1300,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9661</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.911</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.0487</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.1033</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9708</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.8669</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.0431</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.1007</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.9291</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.9595</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.9264</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.973</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.0591</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.1067</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9782</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.9084</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.1031</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,21))</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.9001</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.9154</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.1035</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.9703000000000001</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.8856</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.1018</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9804</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.9146</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.1035</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,650,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.9307</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.8793</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.1015</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,15))</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.9056999999999999</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.0138</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.1089</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,21))</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.9011</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2.0109</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.0617</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.1088</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,25))</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.8994</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2.0135</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.0629</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.1089</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,31))</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.9003</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2.0119</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.06279999999999999</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.1088</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.9253</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.9206</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.0557</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.1038</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>62</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.9071</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.1031</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>63</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.8838</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.0389</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.1017</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>64</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,31))</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.9578</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.8733</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.1011</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>65</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.9676</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.8889</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.102</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>66</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,700,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.9271</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.0489</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.1042</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>67</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.9692</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.9201</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.0485</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.1038</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>72</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,11)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.9337</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1.952</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.1056</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>73</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.9542</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1.9575</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.0481</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.1059</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>74</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.9365</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1.9139</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.1034</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>75</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.9208</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.9566</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.1058</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>76</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.9525</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1.896</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.1024</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>77</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0.9216</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.9155</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.1035</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>78</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.8591</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.0627</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.0726</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.1115</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>79</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0.8591</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2.0627</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.0726</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.1115</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>80</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0.9013</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2.0097</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.0621</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.1087</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>81</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.8766</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.0658</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.1093</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>82</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2.0227</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.06569999999999999</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.1094</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>83</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.8767</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2.0209</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.0658</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.1093</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>84</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.9627</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.1055</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>85</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.9696</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.9436</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.0452</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.1051</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>86</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.8557</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2.0703</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.0726</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.1119</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>87</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0.9112</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2.0688</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.0615</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.1119</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>88</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.8567</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2.0694</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.0726</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.1119</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>89</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.9436</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1.9138</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.0527</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.1034</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>90</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0.9709</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1.9149</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.1035</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>91</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0.9749</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1.9195</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.1038</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>92</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0.9696</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.9477</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.0445</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.1053</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>93</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0.9512</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1.8999</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.1026</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>94</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0.9228</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1.9086</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.06270000000000001</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.1031</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>95</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0.9749</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1.9195</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.1038</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>96</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0.9228</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1.9086</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.06270000000000001</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.1031</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>97</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0.8928</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1.9524</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.1056</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>98</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0.7712</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2.0502</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.07969999999999999</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.1109</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>99</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0.8677</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1.9631</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.1062</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>100</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0.8673999999999999</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1.9694</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.1065</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>101</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0.9404</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1.9038</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.0527</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.1029</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>102</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0.9468</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.9192</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.0506</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.1037</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>103</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0.8753</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.9274</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.1042</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>104</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0.8639</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1.923</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>105</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0.8901</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1.9228</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.0617</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.1039</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>106</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0.9141</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.9229</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.0622</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.1039</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>107</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0.9374</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.8912</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.0539</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.1021</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>108</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0.9540999999999999</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1.9191</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.0488</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.1037</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>109</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0.9509</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.9078</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.1031</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>110</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0.9494</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.9229</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.104</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>111</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0.9254</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.8938</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.1023</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>112</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0.9367</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1.8954</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.1024</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>113</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0.9125</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.9029</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.06279999999999999</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.1028</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>114</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0.9742</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1.8983</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.0412</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.1026</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>115</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0.9246</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.897</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.1025</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>116</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0.9384</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1.8924</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.1022</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>117</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0.9127</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.9018</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.06279999999999999</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.1028</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>118</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0.9006</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.904</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.0608</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.1029</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>119</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0.8892</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1.994</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.0683</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.1079</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>120</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0.9193</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.9885</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.1076</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>121</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9540999999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.9191</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.0488</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.1037</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>122</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0.9384</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.8924</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.1022</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>123</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0.8696</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.968</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.1065</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>124</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0.8696</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.968</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.0663</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.1065</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>125</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0.8656</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.9692</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.0682</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.1065</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>126</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0.9384</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.8923</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.0529</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.1022</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>127</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3'), list('sder',c(2,4,31))</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0.9215</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.9147</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.0586</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.1035</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>172</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>list('snv',''),list('sder',c(1,3,9)),list('red',c(10,10,1))</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0.9704</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.8947</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.1023</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>173</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,4,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0.9367</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.8976</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.1025</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>C20.0</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>174</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2,4,25))</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0.9455</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.9152</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.1035</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/C20.0/RANDOMSEARCH_DETAILS_C20.0.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/C20.0/RANDOMSEARCH_DETAILS_C20.0.xlsx
@@ -474,20 +474,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.977</v>
+        <v>0.9649</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9111</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0401</v>
+        <v>0.0466</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1033</v>
+        <v>0.1068</v>
       </c>
     </row>
     <row r="3">
@@ -506,20 +506,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9678</v>
+        <v>0.9696</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8888</v>
+        <v>0.0767</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0474</v>
+        <v>0.0471</v>
       </c>
       <c r="H3" t="n">
-        <v>0.102</v>
+        <v>0.1064</v>
       </c>
     </row>
     <row r="4">
@@ -538,20 +538,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.8928</v>
+        <v>0.8833</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9524</v>
+        <v>0.073</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0599</v>
+        <v>0.0641</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1056</v>
+        <v>0.1066</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +570,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9051</v>
+        <v>0.9112</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0174</v>
+        <v>-0.0387</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0619</v>
+        <v>0.0608</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1091</v>
+        <v>0.1128</v>
       </c>
     </row>
     <row r="6">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8813</v>
+        <v>0.8809</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0124</v>
+        <v>-0.0591</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1089</v>
+        <v>0.1139</v>
       </c>
     </row>
     <row r="7">
@@ -634,20 +634,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9191</v>
+        <v>0.923</v>
       </c>
       <c r="F7" t="n">
-        <v>1.997</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0594</v>
+        <v>0.0559</v>
       </c>
       <c r="H7" t="n">
-        <v>0.108</v>
+        <v>0.1102</v>
       </c>
     </row>
     <row r="8">
@@ -666,20 +666,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9015</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9964</v>
+        <v>-0.0272</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0554</v>
+        <v>0.0636</v>
       </c>
       <c r="H8" t="n">
-        <v>0.108</v>
+        <v>0.1122</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9502</v>
+        <v>0.9701</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9159</v>
+        <v>0.0583</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0519</v>
+        <v>0.0481</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1036</v>
+        <v>0.1074</v>
       </c>
     </row>
     <row r="10">
@@ -730,20 +730,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.8978</v>
+        <v>0.892</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0276</v>
+        <v>-0.0377</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0623</v>
+        <v>0.0645</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1097</v>
+        <v>0.1128</v>
       </c>
     </row>
     <row r="11">
@@ -762,20 +762,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9669</v>
+        <v>0.8963</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0151</v>
+        <v>-0.0206</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0455</v>
+        <v>0.0636</v>
       </c>
       <c r="H11" t="n">
-        <v>0.109</v>
+        <v>0.1118</v>
       </c>
     </row>
     <row r="12">
@@ -794,20 +794,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9328</v>
+        <v>0.8914</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0047</v>
+        <v>-0.0241</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0557</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1085</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="13">
@@ -826,20 +826,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9271</v>
+        <v>0.8919</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0152</v>
+        <v>-0.0264</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0569</v>
+        <v>0.0643</v>
       </c>
       <c r="H13" t="n">
-        <v>0.109</v>
+        <v>0.1121</v>
       </c>
     </row>
     <row r="14">
@@ -858,20 +858,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.8961</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0155</v>
+        <v>-0.0205</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0613</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.109</v>
+        <v>0.1118</v>
       </c>
     </row>
     <row r="15">
@@ -890,20 +890,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9321</v>
+        <v>0.8912</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0078</v>
+        <v>-0.0287</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0558</v>
+        <v>0.0641</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1086</v>
+        <v>0.1123</v>
       </c>
     </row>
     <row r="16">
@@ -926,16 +926,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8981</v>
+        <v>0.89</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0188</v>
+        <v>-0.0225</v>
       </c>
       <c r="G16" t="n">
-        <v>0.062</v>
+        <v>0.0644</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1092</v>
+        <v>0.1119</v>
       </c>
     </row>
     <row r="17">
@@ -954,20 +954,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.927</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0098</v>
+        <v>-0.0241</v>
       </c>
       <c r="G17" t="n">
-        <v>0.057</v>
+        <v>0.0644</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1087</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="18">
@@ -986,20 +986,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9432</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9115</v>
+        <v>0.0887</v>
       </c>
       <c r="G18" t="n">
-        <v>0.053</v>
+        <v>0.0541</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1033</v>
+        <v>0.1057</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9384</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9144</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0402</v>
+        <v>0.0544</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1035</v>
+        <v>0.1062</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9157</v>
+        <v>0.9344</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9387</v>
+        <v>0.0727</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0604</v>
+        <v>0.0557</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1048</v>
+        <v>0.1066</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9041</v>
+        <v>0.9389</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9377</v>
+        <v>0.0704</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0614</v>
+        <v>0.0537</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1048</v>
+        <v>0.1067</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.907</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9422</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>0.061</v>
+        <v>0.0623</v>
       </c>
       <c r="H22" t="n">
-        <v>0.105</v>
+        <v>0.1072</v>
       </c>
     </row>
     <row r="23">
@@ -1150,16 +1150,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9288999999999999</v>
+        <v>0.9332</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9345</v>
+        <v>0.0507</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0556</v>
+        <v>0.0553</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1046</v>
+        <v>0.1078</v>
       </c>
     </row>
     <row r="24">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9206</v>
+        <v>0.9276</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9166</v>
+        <v>0.0697</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0561</v>
+        <v>0.0554</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1036</v>
+        <v>0.1068</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9322</v>
+        <v>0.9715</v>
       </c>
       <c r="F25" t="n">
-        <v>1.936</v>
+        <v>0.043</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0562</v>
+        <v>0.0409</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1047</v>
+        <v>0.1083</v>
       </c>
     </row>
     <row r="26">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9146</v>
+        <v>0.9664</v>
       </c>
       <c r="F26" t="n">
-        <v>1.9538</v>
+        <v>0.062</v>
       </c>
       <c r="G26" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0489</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1057</v>
+        <v>0.1072</v>
       </c>
     </row>
     <row r="27">
@@ -1278,16 +1278,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9472</v>
+        <v>0.9416</v>
       </c>
       <c r="F27" t="n">
-        <v>1.9324</v>
+        <v>0.0881</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0522</v>
+        <v>0.0533</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1045</v>
+        <v>0.1057</v>
       </c>
     </row>
     <row r="28">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9422</v>
+        <v>0.9442</v>
       </c>
       <c r="F28" t="n">
-        <v>1.9124</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0532</v>
+        <v>0.0542</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1034</v>
+        <v>0.1051</v>
       </c>
     </row>
     <row r="29">
@@ -1338,20 +1338,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.947</v>
+        <v>0.9715</v>
       </c>
       <c r="F29" t="n">
-        <v>1.908</v>
+        <v>0.0837</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0517</v>
+        <v>0.0426</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1031</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9384</v>
+        <v>0.9341</v>
       </c>
       <c r="F30" t="n">
-        <v>1.928</v>
+        <v>0.0761</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0574</v>
+        <v>0.0558</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1042</v>
+        <v>0.1064</v>
       </c>
     </row>
     <row r="31">
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9115</v>
+        <v>0.9127</v>
       </c>
       <c r="F31" t="n">
-        <v>1.9432</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0609</v>
+        <v>0.0613</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1051</v>
+        <v>0.1072</v>
       </c>
     </row>
     <row r="32">
@@ -1434,20 +1434,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9529</v>
+        <v>0.9281</v>
       </c>
       <c r="F32" t="n">
-        <v>1.9412</v>
+        <v>0.0665</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0494</v>
+        <v>0.0568</v>
       </c>
       <c r="H32" t="n">
-        <v>0.105</v>
+        <v>0.1069</v>
       </c>
     </row>
     <row r="33">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9717</v>
+        <v>0.947</v>
       </c>
       <c r="F33" t="n">
-        <v>1.9295</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0417</v>
+        <v>0.0508</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1043</v>
+        <v>0.1071</v>
       </c>
     </row>
     <row r="34">
@@ -1498,20 +1498,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9282</v>
+        <v>0.958</v>
       </c>
       <c r="F34" t="n">
-        <v>1.9185</v>
+        <v>0.0599</v>
       </c>
       <c r="G34" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0553</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1037</v>
+        <v>0.1073</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9224</v>
+        <v>0.9603</v>
       </c>
       <c r="F35" t="n">
-        <v>1.9148</v>
+        <v>0.0482</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0653</v>
+        <v>0.0526</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1035</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="36">
@@ -1562,20 +1562,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9499</v>
+        <v>0.9559</v>
       </c>
       <c r="F36" t="n">
-        <v>1.9035</v>
+        <v>0.0476</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0522</v>
+        <v>0.0499</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1029</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="37">
@@ -1594,20 +1594,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="F37" t="n">
-        <v>1.9082</v>
+        <v>0.0746</v>
       </c>
       <c r="G37" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0615</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1031</v>
+        <v>0.1065</v>
       </c>
     </row>
     <row r="38">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9157</v>
+        <v>0.9827</v>
       </c>
       <c r="F38" t="n">
-        <v>1.8999</v>
+        <v>0.079</v>
       </c>
       <c r="G38" t="n">
-        <v>0.063</v>
+        <v>0.0397</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1026</v>
+        <v>0.1062</v>
       </c>
     </row>
     <row r="39">
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9494</v>
+        <v>0.9633</v>
       </c>
       <c r="F39" t="n">
-        <v>1.9022</v>
+        <v>0.0848</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0526</v>
+        <v>0.0484</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1028</v>
+        <v>0.1059</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.899</v>
+        <v>0.9761</v>
       </c>
       <c r="F40" t="n">
-        <v>1.8992</v>
+        <v>0.103</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0653</v>
+        <v>0.0402</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1026</v>
+        <v>0.1048</v>
       </c>
     </row>
     <row r="41">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9649</v>
+        <v>0.9728</v>
       </c>
       <c r="F41" t="n">
-        <v>1.9206</v>
+        <v>0.0621</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0475</v>
+        <v>0.044</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1038</v>
+        <v>0.1072</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9223</v>
+        <v>0.961</v>
       </c>
       <c r="F42" t="n">
-        <v>1.9194</v>
+        <v>0.0534</v>
       </c>
       <c r="G42" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0525</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1038</v>
+        <v>0.1077</v>
       </c>
     </row>
     <row r="43">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9513</v>
+        <v>0.9564</v>
       </c>
       <c r="F43" t="n">
-        <v>1.8996</v>
+        <v>0.0524</v>
       </c>
       <c r="G43" t="n">
-        <v>0.052</v>
+        <v>0.0498</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1026</v>
+        <v>0.1077</v>
       </c>
     </row>
     <row r="44">
@@ -1818,20 +1818,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.9224</v>
       </c>
       <c r="F44" t="n">
-        <v>1.9088</v>
+        <v>0.0876</v>
       </c>
       <c r="G44" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0614</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1031</v>
+        <v>0.1057</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9157</v>
+        <v>0.923</v>
       </c>
       <c r="F45" t="n">
-        <v>1.9001</v>
+        <v>0.0945</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0631</v>
+        <v>0.0599</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1027</v>
+        <v>0.1053</v>
       </c>
     </row>
     <row r="46">
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9512</v>
+        <v>0.953</v>
       </c>
       <c r="F46" t="n">
-        <v>1.9076</v>
+        <v>0.0735</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0498</v>
+        <v>0.0508</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1031</v>
+        <v>0.1065</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9004</v>
+        <v>0.9533</v>
       </c>
       <c r="F47" t="n">
-        <v>1.9064</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0654</v>
+        <v>0.0497</v>
       </c>
       <c r="H47" t="n">
-        <v>0.103</v>
+        <v>0.1059</v>
       </c>
     </row>
     <row r="48">
@@ -1950,16 +1950,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9318</v>
+        <v>0.9298</v>
       </c>
       <c r="F48" t="n">
-        <v>1.9186</v>
+        <v>0.0475</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0592</v>
+        <v>0.0594</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1037</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="49">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9661</v>
+        <v>0.9358</v>
       </c>
       <c r="F49" t="n">
-        <v>1.911</v>
+        <v>0.0555</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0487</v>
+        <v>0.0583</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1033</v>
+        <v>0.1076</v>
       </c>
     </row>
     <row r="50">
@@ -2010,20 +2010,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9708</v>
+        <v>0.9478</v>
       </c>
       <c r="F50" t="n">
-        <v>1.8669</v>
+        <v>0.0737</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0431</v>
+        <v>0.0544</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1007</v>
+        <v>0.1065</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.9291</v>
+        <v>0.9614</v>
       </c>
       <c r="F51" t="n">
-        <v>1.9595</v>
+        <v>0.0293</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0583</v>
+        <v>0.0477</v>
       </c>
       <c r="H51" t="n">
-        <v>0.106</v>
+        <v>0.1091</v>
       </c>
     </row>
     <row r="52">
@@ -2074,20 +2074,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.9264</v>
+        <v>0.9295</v>
       </c>
       <c r="F52" t="n">
-        <v>1.973</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0591</v>
+        <v>0.0596</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1067</v>
+        <v>0.1102</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9782</v>
+        <v>0.9139</v>
       </c>
       <c r="F53" t="n">
-        <v>1.9084</v>
+        <v>0.0893</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0424</v>
+        <v>0.058</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1031</v>
+        <v>0.1056</v>
       </c>
     </row>
     <row r="54">
@@ -2138,20 +2138,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.9001</v>
+        <v>0.9216</v>
       </c>
       <c r="F54" t="n">
-        <v>1.9154</v>
+        <v>0.0463</v>
       </c>
       <c r="G54" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0605</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1035</v>
+        <v>0.1081</v>
       </c>
     </row>
     <row r="55">
@@ -2170,20 +2170,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>1.8856</v>
+        <v>0.0883</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0425</v>
+        <v>0.0559</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1018</v>
+        <v>0.1057</v>
       </c>
     </row>
     <row r="56">
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9804</v>
+        <v>0.9777</v>
       </c>
       <c r="F56" t="n">
-        <v>1.9146</v>
+        <v>0.1056</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0404</v>
+        <v>0.0396</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1035</v>
+        <v>0.1047</v>
       </c>
     </row>
     <row r="57">
@@ -2234,20 +2234,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9307</v>
+        <v>0.9781</v>
       </c>
       <c r="F57" t="n">
-        <v>1.8793</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0588</v>
+        <v>0.0412</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1015</v>
+        <v>0.1062</v>
       </c>
     </row>
     <row r="58">
@@ -2266,20 +2266,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>2.0138</v>
+        <v>-0.06</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0612</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1089</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="59">
@@ -2298,20 +2298,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.9011</v>
+        <v>0.8064</v>
       </c>
       <c r="F59" t="n">
-        <v>2.0109</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0617</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1088</v>
+        <v>0.1141</v>
       </c>
     </row>
     <row r="60">
@@ -2330,20 +2330,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.8994</v>
+        <v>0.8254</v>
       </c>
       <c r="F60" t="n">
-        <v>2.0135</v>
+        <v>-0.0649</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0629</v>
+        <v>0.0741</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1089</v>
+        <v>0.1142</v>
       </c>
     </row>
     <row r="61">
@@ -2362,20 +2362,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.9003</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>2.0119</v>
+        <v>-0.0615</v>
       </c>
       <c r="G61" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0759</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1088</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="62">
@@ -2394,20 +2394,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.9253</v>
+        <v>0.9727</v>
       </c>
       <c r="F62" t="n">
-        <v>1.9206</v>
+        <v>0.0755</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0557</v>
+        <v>0.0406</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1038</v>
+        <v>0.1064</v>
       </c>
     </row>
     <row r="63">
@@ -2426,20 +2426,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.9435</v>
+        <v>0.9395</v>
       </c>
       <c r="F63" t="n">
-        <v>1.9071</v>
+        <v>0.0828</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0525</v>
+        <v>0.0538</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1031</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="64">
@@ -2458,20 +2458,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.9764</v>
+        <v>0.9306</v>
       </c>
       <c r="F64" t="n">
-        <v>1.8838</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0389</v>
+        <v>0.0544</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1017</v>
+        <v>0.1051</v>
       </c>
     </row>
     <row r="65">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.9578</v>
+        <v>0.9244</v>
       </c>
       <c r="F65" t="n">
-        <v>1.8733</v>
+        <v>0.0987</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0443</v>
+        <v>0.0556</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1011</v>
+        <v>0.1051</v>
       </c>
     </row>
     <row r="66">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9676</v>
+        <v>0.9647</v>
       </c>
       <c r="F66" t="n">
-        <v>1.8889</v>
+        <v>0.0576</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0476</v>
+        <v>0.0491</v>
       </c>
       <c r="H66" t="n">
-        <v>0.102</v>
+        <v>0.1075</v>
       </c>
     </row>
     <row r="67">
@@ -2554,20 +2554,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.963</v>
+        <v>0.9104</v>
       </c>
       <c r="F67" t="n">
-        <v>1.9271</v>
+        <v>0.0422</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0489</v>
+        <v>0.0645</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1042</v>
+        <v>0.1083</v>
       </c>
     </row>
     <row r="68">
@@ -2586,20 +2586,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9692</v>
+        <v>0.9788</v>
       </c>
       <c r="F68" t="n">
-        <v>1.9201</v>
+        <v>0.0311</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0485</v>
+        <v>0.0417</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1038</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="69">
@@ -2618,20 +2618,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9337</v>
+        <v>0.9708</v>
       </c>
       <c r="F69" t="n">
-        <v>1.952</v>
+        <v>0.0009</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0551</v>
+        <v>0.0436</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1056</v>
+        <v>0.1106</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9542</v>
+        <v>0.9416</v>
       </c>
       <c r="F70" t="n">
-        <v>1.9575</v>
+        <v>0.0179</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0481</v>
+        <v>0.0533</v>
       </c>
       <c r="H70" t="n">
-        <v>0.1059</v>
+        <v>0.1097</v>
       </c>
     </row>
     <row r="71">
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9365</v>
+        <v>0.9332</v>
       </c>
       <c r="F71" t="n">
-        <v>1.9139</v>
+        <v>0.0456</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0537</v>
+        <v>0.0542</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1034</v>
+        <v>0.1081</v>
       </c>
     </row>
     <row r="72">
@@ -2714,20 +2714,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9208</v>
+        <v>0.9161</v>
       </c>
       <c r="F72" t="n">
-        <v>1.9566</v>
+        <v>-0.0021</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0569</v>
+        <v>0.0621</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1058</v>
+        <v>0.1108</v>
       </c>
     </row>
     <row r="73">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9525</v>
+        <v>0.9262</v>
       </c>
       <c r="F73" t="n">
-        <v>1.896</v>
+        <v>0.0694</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0516</v>
+        <v>0.0665</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1024</v>
+        <v>0.1068</v>
       </c>
     </row>
     <row r="74">
@@ -2778,20 +2778,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9216</v>
+        <v>0.9294</v>
       </c>
       <c r="F74" t="n">
-        <v>1.9155</v>
+        <v>0.0718</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0655</v>
+        <v>0.0606</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1035</v>
+        <v>0.1066</v>
       </c>
     </row>
     <row r="75">
@@ -2814,16 +2814,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.8591</v>
+        <v>0.8486</v>
       </c>
       <c r="F75" t="n">
-        <v>2.0627</v>
+        <v>-0.08</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0726</v>
+        <v>0.0745</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1115</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="76">
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.8591</v>
+        <v>0.8486</v>
       </c>
       <c r="F76" t="n">
-        <v>2.0627</v>
+        <v>-0.08</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0726</v>
+        <v>0.0745</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1115</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="77">
@@ -2874,20 +2874,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.9013</v>
+        <v>0.9143</v>
       </c>
       <c r="F77" t="n">
-        <v>2.0097</v>
+        <v>-0.0584</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0621</v>
+        <v>0.0603</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1087</v>
+        <v>0.1139</v>
       </c>
     </row>
     <row r="78">
@@ -2906,20 +2906,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8766</v>
+        <v>0.9052</v>
       </c>
       <c r="F78" t="n">
-        <v>2.02</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0658</v>
+        <v>0.063</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1093</v>
+        <v>0.1142</v>
       </c>
     </row>
     <row r="79">
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.875</v>
+        <v>0.9041</v>
       </c>
       <c r="F79" t="n">
-        <v>2.0227</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.0635</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1094</v>
+        <v>0.1142</v>
       </c>
     </row>
     <row r="80">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8767</v>
+        <v>0.9052</v>
       </c>
       <c r="F80" t="n">
-        <v>2.0209</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0658</v>
+        <v>0.0631</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1093</v>
+        <v>0.1141</v>
       </c>
     </row>
     <row r="81">
@@ -3002,20 +3002,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.9627</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="F81" t="n">
-        <v>1.95</v>
+        <v>0.0383</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0476</v>
+        <v>0.059</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1055</v>
+        <v>0.1085</v>
       </c>
     </row>
     <row r="82">
@@ -3034,20 +3034,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.9696</v>
+        <v>0.9321</v>
       </c>
       <c r="F82" t="n">
-        <v>1.9436</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0452</v>
+        <v>0.0603</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1051</v>
+        <v>0.1102</v>
       </c>
     </row>
     <row r="83">
@@ -3066,20 +3066,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.8557</v>
+        <v>0.8682</v>
       </c>
       <c r="F83" t="n">
-        <v>2.0703</v>
+        <v>-0.082</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0726</v>
+        <v>0.0718</v>
       </c>
       <c r="H83" t="n">
-        <v>0.1119</v>
+        <v>0.1151</v>
       </c>
     </row>
     <row r="84">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9112</v>
+        <v>0.8678</v>
       </c>
       <c r="F84" t="n">
-        <v>2.0688</v>
+        <v>-0.0769</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0615</v>
+        <v>0.0717</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1119</v>
+        <v>0.1149</v>
       </c>
     </row>
     <row r="85">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.8567</v>
+        <v>0.8685</v>
       </c>
       <c r="F85" t="n">
-        <v>2.0694</v>
+        <v>-0.081</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0726</v>
+        <v>0.0718</v>
       </c>
       <c r="H85" t="n">
-        <v>0.1119</v>
+        <v>0.1151</v>
       </c>
     </row>
     <row r="86">
@@ -3162,20 +3162,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9436</v>
+        <v>0.9759</v>
       </c>
       <c r="F86" t="n">
-        <v>1.9138</v>
+        <v>0.0983</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0527</v>
+        <v>0.0386</v>
       </c>
       <c r="H86" t="n">
-        <v>0.1034</v>
+        <v>0.1051</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9709</v>
+        <v>0.9435</v>
       </c>
       <c r="F87" t="n">
-        <v>1.9149</v>
+        <v>0.0984</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0427</v>
+        <v>0.0519</v>
       </c>
       <c r="H87" t="n">
-        <v>0.1035</v>
+        <v>0.1051</v>
       </c>
     </row>
     <row r="88">
@@ -3226,20 +3226,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9749</v>
+        <v>0.9388</v>
       </c>
       <c r="F88" t="n">
-        <v>1.9195</v>
+        <v>0.0951</v>
       </c>
       <c r="G88" t="n">
-        <v>0.042</v>
+        <v>0.0532</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1038</v>
+        <v>0.1053</v>
       </c>
     </row>
     <row r="89">
@@ -3258,20 +3258,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9696</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="F89" t="n">
-        <v>1.9477</v>
+        <v>0.08</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0445</v>
+        <v>0.0559</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1053</v>
+        <v>0.1062</v>
       </c>
     </row>
     <row r="90">
@@ -3290,20 +3290,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9512</v>
+        <v>0.9564</v>
       </c>
       <c r="F90" t="n">
-        <v>1.8999</v>
+        <v>0.0519</v>
       </c>
       <c r="G90" t="n">
-        <v>0.052</v>
+        <v>0.0498</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1026</v>
+        <v>0.1078</v>
       </c>
     </row>
     <row r="91">
@@ -3322,20 +3322,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9228</v>
+        <v>0.9224</v>
       </c>
       <c r="F91" t="n">
-        <v>1.9086</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="G91" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0614</v>
       </c>
       <c r="H91" t="n">
-        <v>0.1031</v>
+        <v>0.1057</v>
       </c>
     </row>
     <row r="92">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9749</v>
+        <v>0.9388</v>
       </c>
       <c r="F92" t="n">
-        <v>1.9195</v>
+        <v>0.0951</v>
       </c>
       <c r="G92" t="n">
-        <v>0.042</v>
+        <v>0.0532</v>
       </c>
       <c r="H92" t="n">
-        <v>0.1038</v>
+        <v>0.1053</v>
       </c>
     </row>
     <row r="93">
@@ -3386,20 +3386,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9228</v>
+        <v>0.9224</v>
       </c>
       <c r="F93" t="n">
-        <v>1.9086</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="G93" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0614</v>
       </c>
       <c r="H93" t="n">
-        <v>0.1031</v>
+        <v>0.1057</v>
       </c>
     </row>
     <row r="94">
@@ -3418,20 +3418,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.8928</v>
+        <v>0.8833</v>
       </c>
       <c r="F94" t="n">
-        <v>1.9524</v>
+        <v>0.073</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0599</v>
+        <v>0.0641</v>
       </c>
       <c r="H94" t="n">
-        <v>0.1056</v>
+        <v>0.1066</v>
       </c>
     </row>
     <row r="95">
@@ -3454,16 +3454,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.7712</v>
+        <v>0.7638</v>
       </c>
       <c r="F95" t="n">
-        <v>2.0502</v>
+        <v>-0.0188</v>
       </c>
       <c r="G95" t="n">
         <v>0.07969999999999999</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1109</v>
+        <v>0.1117</v>
       </c>
     </row>
     <row r="96">
@@ -3482,20 +3482,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.8677</v>
+        <v>0.8751</v>
       </c>
       <c r="F96" t="n">
-        <v>1.9631</v>
+        <v>0.0688</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0655</v>
+        <v>0.0648</v>
       </c>
       <c r="H96" t="n">
-        <v>0.1062</v>
+        <v>0.1068</v>
       </c>
     </row>
     <row r="97">
@@ -3514,20 +3514,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.8528</v>
       </c>
       <c r="F97" t="n">
-        <v>1.9694</v>
+        <v>0.0696</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0655</v>
+        <v>0.0688</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1065</v>
+        <v>0.1068</v>
       </c>
     </row>
     <row r="98">
@@ -3546,20 +3546,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9404</v>
+        <v>0.9145</v>
       </c>
       <c r="F98" t="n">
-        <v>1.9038</v>
+        <v>0.1099</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0527</v>
+        <v>0.0594</v>
       </c>
       <c r="H98" t="n">
-        <v>0.1029</v>
+        <v>0.1044</v>
       </c>
     </row>
     <row r="99">
@@ -3578,20 +3578,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9468</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>1.9192</v>
+        <v>0.0959</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0506</v>
+        <v>0.0431</v>
       </c>
       <c r="H99" t="n">
-        <v>0.1037</v>
+        <v>0.1052</v>
       </c>
     </row>
     <row r="100">
@@ -3610,20 +3610,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.8753</v>
+        <v>0.8993</v>
       </c>
       <c r="F100" t="n">
-        <v>1.9274</v>
+        <v>0.0835</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0667</v>
+        <v>0.0614</v>
       </c>
       <c r="H100" t="n">
-        <v>0.1042</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.8639</v>
+        <v>0.9292</v>
       </c>
       <c r="F101" t="n">
-        <v>1.923</v>
+        <v>0.0549</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0675</v>
+        <v>0.0556</v>
       </c>
       <c r="H101" t="n">
-        <v>0.104</v>
+        <v>0.1076</v>
       </c>
     </row>
     <row r="102">
@@ -3678,16 +3678,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.8901</v>
+        <v>0.8861</v>
       </c>
       <c r="F102" t="n">
-        <v>1.9228</v>
+        <v>0.0755</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0617</v>
+        <v>0.0633</v>
       </c>
       <c r="H102" t="n">
-        <v>0.1039</v>
+        <v>0.1064</v>
       </c>
     </row>
     <row r="103">
@@ -3706,20 +3706,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9141</v>
+        <v>0.8955</v>
       </c>
       <c r="F103" t="n">
-        <v>1.9229</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="G103" t="n">
-        <v>0.0622</v>
+        <v>0.0667</v>
       </c>
       <c r="H103" t="n">
-        <v>0.1039</v>
+        <v>0.1054</v>
       </c>
     </row>
     <row r="104">
@@ -3738,20 +3738,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9374</v>
+        <v>0.9093</v>
       </c>
       <c r="F104" t="n">
-        <v>1.8912</v>
+        <v>0.1101</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0539</v>
+        <v>0.0621</v>
       </c>
       <c r="H104" t="n">
-        <v>0.1021</v>
+        <v>0.1044</v>
       </c>
     </row>
     <row r="105">
@@ -3774,16 +3774,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="F105" t="n">
-        <v>1.9191</v>
+        <v>0.0707</v>
       </c>
       <c r="G105" t="n">
         <v>0.0488</v>
       </c>
       <c r="H105" t="n">
-        <v>0.1037</v>
+        <v>0.1067</v>
       </c>
     </row>
     <row r="106">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9509</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="F106" t="n">
-        <v>1.9078</v>
+        <v>0.0882</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0493</v>
+        <v>0.0629</v>
       </c>
       <c r="H106" t="n">
-        <v>0.1031</v>
+        <v>0.1057</v>
       </c>
     </row>
     <row r="107">
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9494</v>
+        <v>0.9497</v>
       </c>
       <c r="F107" t="n">
-        <v>1.9229</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0499</v>
+        <v>0.0501</v>
       </c>
       <c r="H107" t="n">
-        <v>0.104</v>
+        <v>0.1065</v>
       </c>
     </row>
     <row r="108">
@@ -3866,20 +3866,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9254</v>
+        <v>0.963</v>
       </c>
       <c r="F108" t="n">
-        <v>1.8938</v>
+        <v>0.0799</v>
       </c>
       <c r="G108" t="n">
-        <v>0.062</v>
+        <v>0.0479</v>
       </c>
       <c r="H108" t="n">
-        <v>0.1023</v>
+        <v>0.1062</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9367</v>
+        <v>0.9253</v>
       </c>
       <c r="F109" t="n">
-        <v>1.8954</v>
+        <v>0.0844</v>
       </c>
       <c r="G109" t="n">
-        <v>0.0532</v>
+        <v>0.0607</v>
       </c>
       <c r="H109" t="n">
-        <v>0.1024</v>
+        <v>0.1059</v>
       </c>
     </row>
     <row r="110">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9125</v>
+        <v>0.9739</v>
       </c>
       <c r="F110" t="n">
-        <v>1.9029</v>
+        <v>0.0873</v>
       </c>
       <c r="G110" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0401</v>
       </c>
       <c r="H110" t="n">
-        <v>0.1028</v>
+        <v>0.1057</v>
       </c>
     </row>
     <row r="111">
@@ -3962,20 +3962,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9742</v>
+        <v>0.9201</v>
       </c>
       <c r="F111" t="n">
-        <v>1.8983</v>
+        <v>0.1094</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0412</v>
+        <v>0.0598</v>
       </c>
       <c r="H111" t="n">
-        <v>0.1026</v>
+        <v>0.1045</v>
       </c>
     </row>
     <row r="112">
@@ -3994,20 +3994,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9246</v>
+        <v>0.9631</v>
       </c>
       <c r="F112" t="n">
-        <v>1.897</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="G112" t="n">
-        <v>0.062</v>
+        <v>0.0477</v>
       </c>
       <c r="H112" t="n">
-        <v>0.1025</v>
+        <v>0.1063</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9384</v>
+        <v>0.9222</v>
       </c>
       <c r="F113" t="n">
-        <v>1.8924</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0529</v>
+        <v>0.061</v>
       </c>
       <c r="H113" t="n">
-        <v>0.1022</v>
+        <v>0.1053</v>
       </c>
     </row>
     <row r="114">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9127</v>
+        <v>0.9737</v>
       </c>
       <c r="F114" t="n">
-        <v>1.9018</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G114" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0403</v>
       </c>
       <c r="H114" t="n">
-        <v>0.1028</v>
+        <v>0.1057</v>
       </c>
     </row>
     <row r="115">
@@ -4094,16 +4094,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9006</v>
+        <v>0.9164</v>
       </c>
       <c r="F115" t="n">
-        <v>1.904</v>
+        <v>0.1166</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0608</v>
+        <v>0.0599</v>
       </c>
       <c r="H115" t="n">
-        <v>0.1029</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="116">
@@ -4122,20 +4122,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.8892</v>
+        <v>0.8585</v>
       </c>
       <c r="F116" t="n">
-        <v>1.994</v>
+        <v>0.006</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0683</v>
+        <v>0.0723</v>
       </c>
       <c r="H116" t="n">
-        <v>0.1079</v>
+        <v>0.1104</v>
       </c>
     </row>
     <row r="117">
@@ -4154,20 +4154,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.9193</v>
+        <v>0.968</v>
       </c>
       <c r="F117" t="n">
-        <v>1.9885</v>
+        <v>0.0358</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0594</v>
+        <v>0.0414</v>
       </c>
       <c r="H117" t="n">
-        <v>0.1076</v>
+        <v>0.1087</v>
       </c>
     </row>
     <row r="118">
@@ -4190,16 +4190,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="F118" t="n">
-        <v>1.9191</v>
+        <v>0.0707</v>
       </c>
       <c r="G118" t="n">
         <v>0.0488</v>
       </c>
       <c r="H118" t="n">
-        <v>0.1037</v>
+        <v>0.1067</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9384</v>
+        <v>0.9222</v>
       </c>
       <c r="F119" t="n">
-        <v>1.8924</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0529</v>
+        <v>0.061</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1022</v>
+        <v>0.1053</v>
       </c>
     </row>
     <row r="120">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.8696</v>
+        <v>0.8237</v>
       </c>
       <c r="F120" t="n">
-        <v>1.968</v>
+        <v>0.04</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0663</v>
+        <v>0.0736</v>
       </c>
       <c r="H120" t="n">
-        <v>0.1065</v>
+        <v>0.1085</v>
       </c>
     </row>
     <row r="121">
@@ -4282,20 +4282,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.8696</v>
+        <v>0.8237</v>
       </c>
       <c r="F121" t="n">
-        <v>1.968</v>
+        <v>0.04</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0663</v>
+        <v>0.0736</v>
       </c>
       <c r="H121" t="n">
-        <v>0.1065</v>
+        <v>0.1085</v>
       </c>
     </row>
     <row r="122">
@@ -4314,20 +4314,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.8656</v>
+        <v>0.9473</v>
       </c>
       <c r="F122" t="n">
-        <v>1.9692</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0682</v>
+        <v>0.0496</v>
       </c>
       <c r="H122" t="n">
-        <v>0.1065</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9384</v>
+        <v>0.9222</v>
       </c>
       <c r="F123" t="n">
-        <v>1.8923</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0529</v>
+        <v>0.061</v>
       </c>
       <c r="H123" t="n">
-        <v>0.1022</v>
+        <v>0.1054</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9215</v>
+        <v>0.9414</v>
       </c>
       <c r="F124" t="n">
-        <v>1.9147</v>
+        <v>0.0959</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0586</v>
+        <v>0.0534</v>
       </c>
       <c r="H124" t="n">
-        <v>0.1035</v>
+        <v>0.1052</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9704</v>
+        <v>0.9759</v>
       </c>
       <c r="F125" t="n">
-        <v>1.8947</v>
+        <v>0.0784</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0421</v>
+        <v>0.0417</v>
       </c>
       <c r="H125" t="n">
-        <v>0.1023</v>
+        <v>0.1063</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9367</v>
+        <v>0.9358</v>
       </c>
       <c r="F126" t="n">
-        <v>1.8976</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G126" t="n">
-        <v>0.057</v>
+        <v>0.0597</v>
       </c>
       <c r="H126" t="n">
-        <v>0.1025</v>
+        <v>0.1068</v>
       </c>
     </row>
     <row r="127">
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.9455</v>
+        <v>0.9146</v>
       </c>
       <c r="F127" t="n">
-        <v>1.9152</v>
+        <v>0.0511</v>
       </c>
       <c r="G127" t="n">
-        <v>0.053</v>
+        <v>0.067</v>
       </c>
       <c r="H127" t="n">
-        <v>0.1035</v>
+        <v>0.1078</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/C20.0/RANDOMSEARCH_DETAILS_C20.0.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/C20.0/RANDOMSEARCH_DETAILS_C20.0.xlsx
@@ -3418,11 +3418,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.8833</v>
+        <v>0.883</v>
       </c>
       <c r="F94" t="n">
         <v>0.073</v>
